--- a/data/trans_bre/IP19C07-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP19C07-Edad-trans_bre.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 77,02</t>
+          <t>0,0; 74,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 0,0</t>
+          <t>-5,95; 0,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 1,04</t>
+          <t>-7,27; 0,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 1,58</t>
+          <t>-5,1; 1,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 3,56</t>
+          <t>-4,93; 4,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 12,36</t>
+          <t>0,05; 12,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 3,24</t>
+          <t>-7,47; 3,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 1,94</t>
+          <t>-5,09; 1,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 0,71</t>
+          <t>-7,75; 1,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 493,23</t>
+          <t>-8,78; 536,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-62,56; 54,12</t>
+          <t>-60,97; 61,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-85,55; 126,26</t>
+          <t>-83,97; 104,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-82,08; 33,1</t>
+          <t>-86,15; 44,42</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 8,93</t>
+          <t>-4,67; 8,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 8,9</t>
+          <t>-6,01; 8,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,86; 15,02</t>
+          <t>1,64; 15,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 11,79</t>
+          <t>0,69; 11,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,5; 63,99</t>
+          <t>-24,34; 63,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-28,43; 72,61</t>
+          <t>-30,21; 77,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,63; 232,11</t>
+          <t>9,29; 256,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,44; 263,09</t>
+          <t>7,4; 246,87</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 5,99</t>
+          <t>-1,62; 5,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 3,38</t>
+          <t>-3,7; 3,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 5,7</t>
+          <t>-0,67; 5,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 5,24</t>
+          <t>-0,94; 5,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 74,04</t>
+          <t>-13,8; 71,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-31,73; 41,55</t>
+          <t>-31,59; 47,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,12; 130,64</t>
+          <t>-10,35; 134,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-15,36; 119,51</t>
+          <t>-14,57; 119,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C07-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP19C07-Edad-trans_bre.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,35</t>
+          <t>0,0; 71,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 0,0</t>
+          <t>-5,77; 0,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 0,45</t>
+          <t>-6,9; 0,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 1,32</t>
+          <t>-5,58; 1,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 4,13</t>
+          <t>-5,2; 3,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 12,9</t>
+          <t>0,28; 13,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 3,2</t>
+          <t>-7,22; 3,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 1,99</t>
+          <t>-5,09; 1,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 1,06</t>
+          <t>-7,39; 0,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 536,99</t>
+          <t>-4,65; 560,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-60,97; 61,92</t>
+          <t>-62,13; 75,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-83,97; 104,95</t>
+          <t>-84,7; 86,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-86,15; 44,42</t>
+          <t>-86,32; 48,01</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 8,87</t>
+          <t>-4,6; 8,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 8,9</t>
+          <t>-4,88; 8,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 15,27</t>
+          <t>1,62; 15,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 11,0</t>
+          <t>1,21; 11,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,34; 63,52</t>
+          <t>-22,86; 62,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,21; 77,57</t>
+          <t>-26,36; 70,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,29; 256,42</t>
+          <t>15,02; 267,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,4; 246,87</t>
+          <t>7,5; 242,86</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 5,96</t>
+          <t>-1,33; 5,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 3,63</t>
+          <t>-3,68; 3,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 5,6</t>
+          <t>-0,57; 5,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 5,13</t>
+          <t>-0,93; 5,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 71,75</t>
+          <t>-11,63; 67,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-31,59; 47,55</t>
+          <t>-32,31; 43,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 134,34</t>
+          <t>-10,83; 126,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-14,57; 119,18</t>
+          <t>-15,92; 117,42</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C07-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP19C07-Edad-trans_bre.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,91</t>
+          <t>0,0; 77,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,34</t>
+          <t>-0,36</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-13,1%</t>
+          <t>-14,29%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 0,0</t>
+          <t>-5,14; 0,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 0,78</t>
+          <t>-6,69; 1,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 1,28</t>
+          <t>-5,03; 1,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 3,75</t>
+          <t>-5,08; 3,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3,14</t>
+          <t>-3,71</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-50,24%</t>
+          <t>-55,43%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 13,48</t>
+          <t>0,15; 12,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 3,78</t>
+          <t>-7,68; 3,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 1,6</t>
+          <t>-5,37; 1,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 0,89</t>
+          <t>-8,64; 0,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 560,03</t>
+          <t>-10,75; 493,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-62,13; 75,45</t>
+          <t>-62,56; 54,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-84,7; 86,66</t>
+          <t>-85,55; 126,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-86,32; 48,01</t>
+          <t>-84,72; 22,7</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,11</t>
+          <t>6,14</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>90,7%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 8,85</t>
+          <t>-4,34; 8,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 8,41</t>
+          <t>-5,52; 8,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 15,46</t>
+          <t>1,86; 15,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 11,58</t>
+          <t>1,02; 12,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,86; 62,76</t>
+          <t>-21,5; 63,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-26,36; 70,46</t>
+          <t>-28,43; 72,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,02; 267,01</t>
+          <t>10,63; 232,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,5; 242,86</t>
+          <t>8,08; 254,79</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,0</t>
+          <t>1,89</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>31,17%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 5,87</t>
+          <t>-1,57; 5,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 3,59</t>
+          <t>-3,53; 3,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 5,75</t>
+          <t>-0,68; 5,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 5,24</t>
+          <t>-1,33; 5,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 67,62</t>
+          <t>-13,72; 74,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-32,31; 43,71</t>
+          <t>-31,73; 41,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 126,84</t>
+          <t>-12,12; 130,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-15,92; 117,42</t>
+          <t>-19,25; 111,24</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C07-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP19C07-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,151 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>19,67</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>19.67435395173791</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 77,02</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>77.01644129621378</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-1,64</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-2,35</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-1,81</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,36</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-70,94%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-64,35%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-14,29%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-5,14; 0,0</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-6,69; 1,04</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-5,03; 1,58</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-5,08; 3,79</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-1.642390205612603</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-2.347343282175966</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-1.808586025204072</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.3647674364120314</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.7094236215254133</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.6435104424883844</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.1429386735681047</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>6,39</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-1,86</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,69</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-3,71</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>136,62%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-21,25%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-40,17%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-55,43%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-5.137519044364455</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-6.690588529391994</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-5.026941614431164</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-5.079979671555098</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,15; 12,36</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-7,68; 3,24</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-5,37; 1,94</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-8,64; 0,19</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-10,75; 493,23</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-62,56; 54,12</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-85,55; 126,26</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-84,72; 22,7</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.041703962394805</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.580200000544521</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>3.788635167459598</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +771,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,8</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,58</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8,22</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6,14</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,46%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,36%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>90,46%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>90,7%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>6.391204908809997</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-1.85729203203429</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.692697015411735</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-3.705433326160032</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>1.366243891174374</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.2124694710027611</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.4017287493760858</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.5543050149849454</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-4,34; 8,93</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-5,52; 8,9</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1,86; 15,02</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1,02; 12,04</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-21,5; 63,99</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-28,43; 72,61</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>10,63; 232,11</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>8,08; 254,79</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.1479421172232446</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-7.675220820737986</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-5.370841663940715</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-8.642175275134747</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.1075220831928702</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.625606565448288</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.8554684995248163</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.8472497556080719</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>12.35857586489993</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.241387168946746</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.940224148981426</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.1932955826134163</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>4.932294408344156</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.5411701149820597</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.262580316927262</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.2270050182320937</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1.804251606425491</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1.581803613795774</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>8.222594975721805</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>6.139413962883111</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.1046050928315841</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.1035817723845411</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.9045852423007265</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.9070359315142555</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-4.33588545033502</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-5.518119414436329</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>1.859129423626871</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>1.020743029217598</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.2149954758609058</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.2843113559740602</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>0.1062671550805986</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>0.08077836305801588</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>8.932300761348028</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>8.897416804593535</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>15.01934396451895</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>12.04372497624634</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.6398628489135729</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.726059824421842</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>2.321054267101226</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>2.547851863688892</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2,21</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,2</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,49</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,89</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>22,06%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-2,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>43,9%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>31,17%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-1,57; 5,99</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3,53; 3,38</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,68; 5,7</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-1,33; 5,24</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-13,72; 74,04</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-31,73; 41,55</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-12,12; 130,64</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-19,25; 111,24</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>2.209443056719782</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.1977556594923366</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>2.492728158609042</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1.887195992232203</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.2206185251206326</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.02002037255755853</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.4390193782586358</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.3117351041317086</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.570491495610452</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.526076092321337</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.6764356033568871</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.32959027572911</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.1372428689112504</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.3173231347679196</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.1211794955182598</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.1924690600990381</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>5.989583073221238</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3.377810862091211</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>5.698356638025405</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>5.236165758937696</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.7404025857937637</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.415499378911945</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>1.306370642095557</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>1.112411933945461</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1069,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
